--- a/experiments/results/resnet18/CIFAR-100/ReAct/adaptive/avg/results.xlsx
+++ b/experiments/results/resnet18/CIFAR-100/ReAct/adaptive/avg/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -813,6 +813,202 @@
       <c r="O9" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=0.1,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>96.91</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>85.86</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>73.77</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>93.93000000000001</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>96.01000000000001</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>89.88</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>90.02</v>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.8,scale_th=0.1,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>72.48999999999999</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>53.18</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>89.18000000000001</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>95.58</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>89.28</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>44.33</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>89.47</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.7,scale_th=0.1,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>96.98</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>74.54000000000001</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>89.72</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>93.97</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>96.25</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>47.47</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>90.09</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>41.03</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>90.26000000000001</v>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.9,scale_th=0.1,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>96.88</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>82.56999999999999</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>50.83</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>93.67</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>48.11</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>90.01000000000001</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>90.31999999999999</v>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=0.1,type=avg</t>
         </is>
       </c>
     </row>
